--- a/data/trans_camb/P29A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P29A_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 1,78</t>
+          <t>-8,85; 1,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 5,18</t>
+          <t>-5,64; 5,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,79; -2,43</t>
+          <t>-14,23; -2,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 2,51</t>
+          <t>-6,74; 2,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 7,0</t>
+          <t>-2,06; 7,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 4,25</t>
+          <t>-4,38; 4,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 0,89</t>
+          <t>-6,73; 0,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 4,41</t>
+          <t>-2,83; 5,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,43; -0,47</t>
+          <t>-8,2; -0,48</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 3,04</t>
+          <t>-13,88; 3,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 8,73</t>
+          <t>-8,94; 8,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,98; -4,25</t>
+          <t>-22,57; -3,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,01; 11,56</t>
+          <t>-25,62; 11,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 32,64</t>
+          <t>-8,01; 34,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 20,28</t>
+          <t>-16,91; 19,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 2,22</t>
+          <t>-15,39; 2,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 10,89</t>
+          <t>-6,48; 12,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,98; -1,03</t>
+          <t>-18,75; -1,27</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 1,63</t>
+          <t>-7,83; 1,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 0,66</t>
+          <t>-9,44; -0,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-37,54; -6,35</t>
+          <t>-39,25; -6,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 2,4</t>
+          <t>-5,81; 2,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 7,01</t>
+          <t>-1,49; 6,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,97; -1,3</t>
+          <t>-9,12; -0,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 0,67</t>
+          <t>-5,68; 0,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 2,39</t>
+          <t>-4,3; 2,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-21,98; -5,69</t>
+          <t>-20,76; -5,5</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 2,92</t>
+          <t>-12,93; 2,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 1,21</t>
+          <t>-15,35; -0,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,17; -11,26</t>
+          <t>-67,69; -10,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 9,58</t>
+          <t>-20,46; 9,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 29,03</t>
+          <t>-5,52; 28,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,49; -5,37</t>
+          <t>-32,36; -4,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 1,63</t>
+          <t>-13,04; 1,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 5,9</t>
+          <t>-9,72; 5,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-50,74; -13,97</t>
+          <t>-49,64; -13,17</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,75; 16,14</t>
+          <t>4,57; 16,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 14,28</t>
+          <t>3,34; 14,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 6,81</t>
+          <t>-4,87; 6,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 9,87</t>
+          <t>1,1; 10,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,88; 14,74</t>
+          <t>5,5; 14,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,15; 54,24</t>
+          <t>4,0; 50,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 11,63</t>
+          <t>4,01; 11,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,49; 12,93</t>
+          <t>5,9; 12,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 34,07</t>
+          <t>1,89; 33,21</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,72; 38,45</t>
+          <t>9,53; 38,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,85; 33,66</t>
+          <t>6,67; 34,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 16,02</t>
+          <t>-9,95; 16,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,69; 59,82</t>
+          <t>5,57; 63,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,95; 93,82</t>
+          <t>28,75; 89,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,51; 322,36</t>
+          <t>21,3; 293,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,05; 38,79</t>
+          <t>12,17; 39,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,86; 43,5</t>
+          <t>18,03; 44,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,52; 112,67</t>
+          <t>5,52; 111,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 7,39</t>
+          <t>-1,91; 7,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 11,09</t>
+          <t>1,6; 10,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,2; -1,06</t>
+          <t>-10,34; -0,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 7,08</t>
+          <t>-1,05; 7,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,98; 14,14</t>
+          <t>5,72; 14,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 2,67</t>
+          <t>-7,16; 2,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 5,81</t>
+          <t>-0,08; 6,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,89; 11,44</t>
+          <t>4,77; 11,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,54; -0,22</t>
+          <t>-8,42; -0,6</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 14,33</t>
+          <t>-3,38; 14,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,06; 21,68</t>
+          <t>2,73; 20,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,78; -1,98</t>
+          <t>-19,12; -1,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 27,82</t>
+          <t>-3,95; 26,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,9; 54,55</t>
+          <t>18,29; 53,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,68; 10,26</t>
+          <t>-24,06; 9,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 15,01</t>
+          <t>-0,2; 16,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,68; 29,32</t>
+          <t>11,39; 28,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-20,88; -0,66</t>
+          <t>-20,29; -1,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,64</t>
+          <t>-1,45; 3,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 4,36</t>
+          <t>-0,47; 4,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,95; -4,75</t>
+          <t>-20,69; -4,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,27</t>
+          <t>-0,99; 3,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,07; 8,28</t>
+          <t>4,07; 8,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 16,42</t>
+          <t>-1,57; 16,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,7</t>
+          <t>-0,72; 2,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,8</t>
+          <t>2,34; 5,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 3,74</t>
+          <t>-6,39; 3,24</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 6,76</t>
+          <t>-2,6; 6,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 8,11</t>
+          <t>-0,84; 8,57</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-34,03; -8,72</t>
+          <t>-37,37; -8,77</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 13,86</t>
+          <t>-3,95; 13,41</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>15,98; 35,07</t>
+          <t>16,05; 35,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 67,86</t>
+          <t>-6,29; 66,32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 6,94</t>
+          <t>-1,81; 7,22</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5,72; 15,1</t>
+          <t>5,77; 14,83</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 9,37</t>
+          <t>-16,09; 8,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P29A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P29A_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-8,17</t>
+          <t>-9,44</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,0</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,55</t>
+          <t>-5,18</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 1,98</t>
+          <t>-9,5; 1,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 5,25</t>
+          <t>-5,49; 5,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,23; -2,18</t>
+          <t>-15,05; -3,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 2,54</t>
+          <t>-6,31; 2,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 7,31</t>
+          <t>-1,83; 7,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 4,13</t>
+          <t>-4,06; 3,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 0,81</t>
+          <t>-7,16; 0,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 5,0</t>
+          <t>-3,26; 4,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,2; -0,48</t>
+          <t>-8,92; -1,68</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-13,45%</t>
+          <t>-15,52%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-0,02%</t>
+          <t>-0,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-10,76%</t>
+          <t>-12,27%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 3,53</t>
+          <t>-15,03; 2,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 8,91</t>
+          <t>-8,63; 8,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,57; -3,73</t>
+          <t>-23,78; -6,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 11,9</t>
+          <t>-24,9; 11,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 34,63</t>
+          <t>-7,25; 34,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 19,73</t>
+          <t>-15,37; 18,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 2,02</t>
+          <t>-16,26; 0,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 12,39</t>
+          <t>-7,23; 11,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,75; -1,27</t>
+          <t>-20,24; -4,16</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-18,53</t>
+          <t>-10,65</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,01</t>
+          <t>-5,18</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-10,63</t>
+          <t>-7,95</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 1,55</t>
+          <t>-7,95; 1,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,44; -0,26</t>
+          <t>-9,01; 0,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-39,25; -6,28</t>
+          <t>-15,48; -6,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 2,4</t>
+          <t>-5,48; 2,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 6,84</t>
+          <t>-1,78; 6,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -0,93</t>
+          <t>-8,89; -1,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 0,73</t>
+          <t>-6,26; 0,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 2,1</t>
+          <t>-4,18; 1,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-20,76; -5,5</t>
+          <t>-11,2; -4,76</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-31,65%</t>
+          <t>-18,18%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-19,21%</t>
+          <t>-19,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-25,19%</t>
+          <t>-18,83%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 2,75</t>
+          <t>-12,88; 3,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,35; -0,4</t>
+          <t>-14,67; 1,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,69; -10,88</t>
+          <t>-25,48; -10,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 9,84</t>
+          <t>-19,4; 9,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 28,3</t>
+          <t>-6,18; 26,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,36; -4,08</t>
+          <t>-31,44; -6,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 1,67</t>
+          <t>-13,97; 0,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 5,12</t>
+          <t>-9,48; 4,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-49,64; -13,17</t>
+          <t>-25,44; -11,49</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>-0,42</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,46</t>
+          <t>6,91</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11,38</t>
+          <t>3,32</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 16,42</t>
+          <t>4,88; 16,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,34; 14,62</t>
+          <t>3,92; 15,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 6,78</t>
+          <t>-6,15; 5,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,14</t>
+          <t>1,16; 10,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,5; 14,01</t>
+          <t>5,77; 14,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,0; 50,22</t>
+          <t>3,06; 10,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,01; 11,65</t>
+          <t>4,02; 11,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,9; 12,97</t>
+          <t>5,57; 12,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 33,21</t>
+          <t>-0,38; 6,79</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>-0,91%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>125,29%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,53; 38,83</t>
+          <t>9,99; 37,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,67; 34,48</t>
+          <t>7,95; 35,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 16,1</t>
+          <t>-12,76; 12,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,57; 63,75</t>
+          <t>5,65; 64,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,75; 89,36</t>
+          <t>29,16; 89,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,3; 293,78</t>
+          <t>13,71; 66,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,17; 39,48</t>
+          <t>12,18; 38,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,03; 44,07</t>
+          <t>16,1; 42,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,52; 111,89</t>
+          <t>-1,05; 22,84</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-5,72</t>
+          <t>-6,56</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,69</t>
+          <t>-3,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 7,5</t>
+          <t>-1,84; 7,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 10,58</t>
+          <t>1,94; 10,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,34; -0,63</t>
+          <t>-11,44; -1,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 7,11</t>
+          <t>-0,67; 6,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,72; 14,29</t>
+          <t>5,44; 14,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 2,73</t>
+          <t>-3,74; 3,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 6,35</t>
+          <t>-0,2; 6,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,77; 11,26</t>
+          <t>4,79; 11,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,42; -0,6</t>
+          <t>-6,26; -0,15</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-10,66%</t>
+          <t>-12,23%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-4,57%</t>
+          <t>-0,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-9,2%</t>
+          <t>-8,1%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 14,27</t>
+          <t>-3,34; 14,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,73; 20,38</t>
+          <t>3,5; 21,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,12; -1,26</t>
+          <t>-20,69; -3,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 26,21</t>
+          <t>-2,29; 26,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,29; 53,63</t>
+          <t>18,19; 53,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-24,06; 9,96</t>
+          <t>-12,53; 13,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 16,41</t>
+          <t>-0,49; 16,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,39; 28,91</t>
+          <t>11,6; 28,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-20,29; -1,51</t>
+          <t>-15,06; -0,49</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-9,18</t>
+          <t>-7,21</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,72</t>
+          <t>-3,71</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,68</t>
+          <t>-1,62; 3,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 4,6</t>
+          <t>-0,44; 4,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,69; -4,75</t>
+          <t>-10,0; -4,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,2</t>
+          <t>-1,1; 3,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,07; 8,4</t>
+          <t>3,84; 8,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 16,54</t>
+          <t>-2,2; 1,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,77</t>
+          <t>-0,83; 2,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,71</t>
+          <t>2,39; 5,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 3,24</t>
+          <t>-5,42; -1,96</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-16,7%</t>
+          <t>-13,13%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>-0,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-6,91%</t>
+          <t>-9,42%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 6,85</t>
+          <t>-2,8; 6,76</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 8,57</t>
+          <t>-0,76; 8,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-37,37; -8,77</t>
+          <t>-17,8; -8,74</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 13,41</t>
+          <t>-4,23; 13,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>16,05; 35,4</t>
+          <t>14,98; 35,18</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 66,32</t>
+          <t>-8,6; 8,25</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 7,22</t>
+          <t>-2,1; 6,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5,77; 14,83</t>
+          <t>5,89; 15,22</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 8,3</t>
+          <t>-13,38; -5,08</t>
         </is>
       </c>
     </row>
